--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486358_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486358_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6994</v>
+        <v>3.9666</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9411</v>
+        <v>5.1466</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2417</v>
+        <v>-1.18</v>
       </c>
       <c r="G2" t="n">
         <v>0.8426</v>
@@ -610,13 +610,13 @@
         <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0705</v>
+        <v>-0.8033</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6044</v>
+        <v>-0.399</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.466</v>
+        <v>-0.4044</v>
       </c>
       <c r="V2" t="n">
         <v>4.7973</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6658</v>
+        <v>2.3682</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3504</v>
+        <v>1.0836</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3154</v>
+        <v>1.2846</v>
       </c>
       <c r="G3" t="n">
         <v>0.1125</v>
@@ -688,13 +688,13 @@
         <v>1.7401</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1044</v>
+        <v>-0.1932</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3341</v>
+        <v>0.0673</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2297</v>
+        <v>-0.2605</v>
       </c>
       <c r="V3" t="n">
         <v>0.7088</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. SIQUIER COSTA</t>
+          <t>L. MENUGE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4093</v>
+        <v>0.4307</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1.5144</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4093</v>
+        <v>-1.0837</v>
       </c>
       <c r="G4" t="n">
-        <v>0.149</v>
+        <v>-1.0769</v>
       </c>
       <c r="H4" t="n">
-        <v>0.149</v>
+        <v>-1.8522</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.7753</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>0.5719</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-0.6903</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.2622</v>
       </c>
       <c r="M4" t="n">
-        <v>0.149</v>
+        <v>-1.6488</v>
       </c>
       <c r="N4" t="n">
-        <v>0.149</v>
+        <v>-1.1619</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0.4869</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.0875</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2603</v>
+        <v>-0.7099</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.1875</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2603</v>
+        <v>-0.5224</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1644</v>
+        <v>0.3456</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9199000000000001</v>
+        <v>1.2552</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.9096</v>
       </c>
       <c r="G5" t="n">
         <v>4.2184</v>
@@ -844,13 +844,13 @@
         <v>1.9576</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.5484</v>
+        <v>-1.3672</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.4182</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7949000000000001</v>
+        <v>-0.9491000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>-0.113</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. MENUGE</t>
+          <t>O. SIQUIER COSTA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0462</v>
+        <v>0.286</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2224</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1762</v>
+        <v>0.286</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0769</v>
+        <v>0.149</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.8522</v>
+        <v>0.149</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7753</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5719</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6903</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2622</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6488</v>
+        <v>0.149</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1619</v>
+        <v>0.149</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4869</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0875</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0875</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0944</v>
+        <v>0.137</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4795</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6149</v>
+        <v>0.137</v>
       </c>
       <c r="V6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3589</v>
+        <v>-0.4184</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2878</v>
+        <v>0.5365</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.9549</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1293</v>
@@ -1000,13 +1000,13 @@
         <v>2.8276</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5262</v>
+        <v>-1.5856</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0154</v>
+        <v>-0.7667</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5107</v>
+        <v>-0.819</v>
       </c>
       <c r="V7" t="n">
         <v>-0.226</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.402</v>
+        <v>-1.6812</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1722</v>
+        <v>-0.4822</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2298</v>
+        <v>-1.1989</v>
       </c>
       <c r="G8" t="n">
         <v>1.1027</v>
@@ -1078,13 +1078,13 @@
         <v>2.6101</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.954</v>
+        <v>-1.2332</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0649</v>
+        <v>-0.3749</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8892</v>
+        <v>-0.8583</v>
       </c>
       <c r="V8" t="n">
         <v>-2.8557</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1519</v>
+        <v>-2.1837</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.435</v>
+        <v>-0.59</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.717</v>
+        <v>-1.5937</v>
       </c>
       <c r="G9" t="n">
         <v>-2.1691</v>
@@ -1156,13 +1156,13 @@
         <v>2.6101</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4778</v>
+        <v>-0.5095</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.1634</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4694</v>
+        <v>-0.3461</v>
       </c>
       <c r="V9" t="n">
         <v>0.2775</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6395</v>
+        <v>-2.8715</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6762</v>
+        <v>-1.2472</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9634</v>
+        <v>-1.6243</v>
       </c>
       <c r="G10" t="n">
         <v>-3.4628</v>
@@ -1234,13 +1234,13 @@
         <v>2.1751</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.086</v>
+        <v>-1.318</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.3124</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.3446</v>
+        <v>-1.0055</v>
       </c>
       <c r="V10" t="n">
         <v>0.8218</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2198</v>
+        <v>-4.0018</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2588</v>
+        <v>-2.01</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.961</v>
+        <v>-1.9918</v>
       </c>
       <c r="G11" t="n">
         <v>0.2212</v>
@@ -1312,13 +1312,13 @@
         <v>1.9576</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6356</v>
+        <v>-1.4177</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8784</v>
+        <v>-0.6297</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7572</v>
+        <v>-0.788</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1952</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.787000000000001</v>
+        <v>-3.759500000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>4.1794</v>
+        <v>5.2069</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.9666</v>
+        <v>-8.9663</v>
       </c>
       <c r="G12" t="n">
         <v>-0.1917</v>
@@ -1390,10 +1390,10 @@
         <v>18.4882</v>
       </c>
       <c r="S12" t="n">
-        <v>-10.0282</v>
+        <v>-9.0006</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.2118</v>
+        <v>-3.1845</v>
       </c>
       <c r="U12" t="n">
         <v>-5.8163</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.8486</v>
+        <v>6.722</v>
       </c>
       <c r="E13" t="n">
-        <v>6.1617</v>
+        <v>6.6087</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3131</v>
+        <v>0.1133</v>
       </c>
       <c r="G13" t="n">
         <v>2.4372</v>
@@ -1468,13 +1468,13 @@
         <v>2.3926</v>
       </c>
       <c r="S13" t="n">
-        <v>0.519</v>
+        <v>1.3925</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1526</v>
+        <v>0.5997</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3664</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>0.9347</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6336</v>
+        <v>3.7151</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4167</v>
+        <v>2.4108</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2169</v>
+        <v>1.3043</v>
       </c>
       <c r="G14" t="n">
         <v>2.7082</v>
@@ -1546,13 +1546,13 @@
         <v>2.8276</v>
       </c>
       <c r="S14" t="n">
-        <v>2.468</v>
+        <v>1.5496</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8362</v>
+        <v>0.8304</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6318</v>
+        <v>0.7192</v>
       </c>
       <c r="V14" t="n">
         <v>-0.7602</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. GONZALEZ CALVO</t>
+          <t>T. BORG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1206</v>
+        <v>2.9828</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4589</v>
+        <v>1.5044</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3383</v>
+        <v>1.4784</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2952</v>
+        <v>0.4922</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2172</v>
+        <v>0.14</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.922</v>
+        <v>0.3522</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0292</v>
+        <v>2.0279</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9527</v>
+        <v>1.7004</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0765</v>
+        <v>0.3275</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7339</v>
+        <v>-1.5357</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2645</v>
+        <v>-1.5604</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9985000000000001</v>
+        <v>0.0247</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.435</v>
+        <v>0.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0875</v>
+        <v>-1.5225</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6525</v>
+        <v>2.3926</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5001</v>
+        <v>1.035</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7571</v>
+        <v>0.4134</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2569</v>
+        <v>0.6216</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7602</v>
+        <v>0.5857</v>
       </c>
       <c r="W15" t="n">
-        <v>0.7602</v>
+        <v>0.5857</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. BORG</t>
+          <t>J. GONZALEZ CALVO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6122</v>
+        <v>1.9587</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4986</v>
+        <v>2.2354</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1137</v>
+        <v>-0.2767</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4922</v>
+        <v>1.2952</v>
       </c>
       <c r="H16" t="n">
-        <v>0.14</v>
+        <v>2.2172</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3522</v>
+        <v>-0.922</v>
       </c>
       <c r="J16" t="n">
-        <v>2.0279</v>
+        <v>2.0292</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7004</v>
+        <v>1.9527</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3275</v>
+        <v>0.0765</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5357</v>
+        <v>-0.7339</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5604</v>
+        <v>0.2645</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0247</v>
+        <v>-0.9985000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>0.87</v>
+        <v>-0.435</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.5225</v>
+        <v>-1.0875</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3926</v>
+        <v>0.6525</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3356</v>
+        <v>0.3383</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5924</v>
+        <v>0.5336</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2568</v>
+        <v>-0.1953</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5857</v>
+        <v>0.7602</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5857</v>
+        <v>0.7602</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ BARRIENTOS</t>
+          <t>M. KAMBA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0265</v>
+        <v>0.0188</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3839</v>
+        <v>-0.0392</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3574</v>
+        <v>0.058</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2206</v>
+        <v>-1.4271</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7938</v>
+        <v>-0.5354</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0144</v>
+        <v>-0.8917</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8647</v>
+        <v>-0.0428</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7117</v>
+        <v>0.511</v>
       </c>
       <c r="L17" t="n">
-        <v>0.153</v>
+        <v>-0.5538</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0854</v>
+        <v>-1.3843</v>
       </c>
       <c r="N17" t="n">
-        <v>0.082</v>
+        <v>-1.0464</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1674</v>
+        <v>-0.3379</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.7401</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.305</v>
+        <v>-0.435</v>
       </c>
       <c r="R17" t="n">
-        <v>1.305</v>
+        <v>2.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>1.7676</v>
+        <v>1.0311</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8242</v>
+        <v>0.4386</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0566</v>
+        <v>0.5924</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.5204</v>
+        <v>-1.3252</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.5204</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. KAMBA</t>
+          <t>A. KUNKEL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3049</v>
+        <v>-0.3425</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4862</v>
+        <v>-0.8135</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1813</v>
+        <v>0.471</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4271</v>
+        <v>-2.5522</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5354</v>
+        <v>-3.844</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8917</v>
+        <v>1.2917</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0428</v>
+        <v>-0.8364</v>
       </c>
       <c r="K18" t="n">
-        <v>0.511</v>
+        <v>-2.4661</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5538</v>
+        <v>1.6296</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3843</v>
+        <v>-1.7158</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0464</v>
+        <v>-1.3779</v>
       </c>
       <c r="O18" t="n">
         <v>-0.3379</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7401</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.435</v>
+        <v>-2.6101</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1751</v>
+        <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7073</v>
+        <v>0.6675</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.1779</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7157</v>
+        <v>0.4897</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.3252</v>
+        <v>2.6297</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.4552</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3252</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X. OROZ URIA</t>
+          <t>M. RODRIGUEZ BARRIENTOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4148</v>
+        <v>-0.8611</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0882</v>
+        <v>0.378</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3266</v>
+        <v>-1.2392</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6617</v>
+        <v>-0.2206</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1405</v>
+        <v>0.7938</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5212</v>
+        <v>-1.0144</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2288</v>
+        <v>0.8647</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3436</v>
+        <v>0.7117</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1147</v>
+        <v>0.153</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4328</v>
+        <v>-1.0854</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7969000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6359</v>
+        <v>-1.1674</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.435</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>1.6819</v>
+        <v>0.8799</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2281</v>
+        <v>0.8184</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4538</v>
+        <v>0.0616</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.5204</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. KUNKEL</t>
+          <t>X. OROZ URIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0632</v>
+        <v>-1.0969</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5958</v>
+        <v>-0.647</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5326</v>
+        <v>-0.4499</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5522</v>
+        <v>-1.6617</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.844</v>
+        <v>-1.1405</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2917</v>
+        <v>-0.5212</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8364</v>
+        <v>-0.2288</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.4661</v>
+        <v>-0.3436</v>
       </c>
       <c r="L20" t="n">
-        <v>1.6296</v>
+        <v>0.1147</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7158</v>
+        <v>-1.4328</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3779</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3379</v>
+        <v>-0.6359</v>
       </c>
       <c r="P20" t="n">
+        <v>-0.435</v>
+      </c>
+      <c r="Q20" t="n">
         <v>-1.0875</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-2.6101</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0531</v>
+        <v>0.9998</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6044</v>
+        <v>0.6694</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5513</v>
+        <v>0.3305</v>
       </c>
       <c r="V20" t="n">
-        <v>2.6297</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.4552</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.1745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.646</v>
+        <v>-1.1064</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6389</v>
+        <v>-0.1919</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.007</v>
+        <v>-0.9146</v>
       </c>
       <c r="G21" t="n">
         <v>-0.4907</v>
@@ -2092,13 +2092,13 @@
         <v>1.7401</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6697</v>
+        <v>1.2092</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0036</v>
+        <v>0.4506</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6661</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>-2.2599</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. UGOCHUKWU</t>
+          <t>A. WINTERING</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7749</v>
+        <v>-2.2771</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4343</v>
+        <v>-0.0393</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3405</v>
+        <v>-2.2379</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.8933</v>
+        <v>1.5045</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.9037</v>
+        <v>-0.1124</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0103</v>
+        <v>1.6168</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6605</v>
+        <v>3.3868</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7752</v>
+        <v>0.9006</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1147</v>
+        <v>2.4862</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2328</v>
+        <v>-1.8823</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1284</v>
+        <v>-1.0129</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1044</v>
+        <v>-0.8694</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.3926</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3926</v>
+        <v>-3.6976</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.7401</v>
       </c>
       <c r="S22" t="n">
-        <v>2.641</v>
+        <v>0.4359</v>
       </c>
       <c r="T22" t="n">
-        <v>1.6187</v>
+        <v>0.2716</v>
       </c>
       <c r="U22" t="n">
-        <v>1.0223</v>
+        <v>0.1643</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.13</v>
+        <v>-2.2599</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.13</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. WINTERING</t>
+          <t>S. UGOCHUKWU</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2508</v>
+        <v>-4.1814</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7098</v>
+        <v>-2.4402</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.541</v>
+        <v>-1.7412</v>
       </c>
       <c r="G23" t="n">
-        <v>1.5045</v>
+        <v>-1.8933</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1124</v>
+        <v>-1.9037</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6168</v>
+        <v>0.0103</v>
       </c>
       <c r="J23" t="n">
-        <v>3.3868</v>
+        <v>-0.6605</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9006</v>
+        <v>-0.7752</v>
       </c>
       <c r="L23" t="n">
-        <v>2.4862</v>
+        <v>0.1147</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8823</v>
+        <v>-1.2328</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0129</v>
+        <v>-1.1284</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8694</v>
+        <v>-0.1044</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.9576</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.6976</v>
+        <v>-2.3926</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7401</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5377999999999999</v>
+        <v>1.2344</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.399</v>
+        <v>0.6129</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1388</v>
+        <v>0.6216</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.2599</v>
+        <v>-1.13</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.2599</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="24">
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>4.786899999999999</v>
+        <v>5.532</v>
       </c>
       <c r="E24" t="n">
-        <v>8.9666</v>
+        <v>8.966199999999997</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.179399999999999</v>
+        <v>-3.4345</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1917000000000011</v>
+        <v>0.1917</v>
       </c>
       <c r="H24" t="n">
         <v>-5.1233</v>
@@ -2305,7 +2305,7 @@
         <v>6.830800000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>9.116100000000001</v>
+        <v>9.116099999999999</v>
       </c>
       <c r="M24" t="n">
         <v>-15.7552</v>
@@ -2326,13 +2326,13 @@
         <v>17.4006</v>
       </c>
       <c r="S24" t="n">
-        <v>10.0281</v>
+        <v>10.7732</v>
       </c>
       <c r="T24" t="n">
-        <v>5.816299999999999</v>
+        <v>5.8165</v>
       </c>
       <c r="U24" t="n">
-        <v>4.2119</v>
+        <v>4.957</v>
       </c>
       <c r="V24" t="n">
         <v>-4.3453</v>
